--- a/storage/exports/rekap_reject_so_09_2025.xlsx
+++ b/storage/exports/rekap_reject_so_09_2025.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\Project\cek-gambar-astras\storage\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5A90B8-C589-4292-95F8-4B195A56E644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D684A824-4EF0-46F6-A7FE-F0F968D2B96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA REJECT FISIK" sheetId="1" r:id="rId1"/>
     <sheet name="DATA REJECT DIGITAL" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DATA REJECT FISIK'!$A$1:$J$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -2786,6 +2789,7 @@
       <c r="J43" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
